--- a/output/pdf_financials_xlsx/CNTR.xlsx
+++ b/output/pdf_financials_xlsx/CNTR.xlsx
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.247956</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.044314</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.05473</v>
       </c>
     </row>
     <row r="93">
@@ -3477,7 +3477,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>2.247956</v>
       </c>
@@ -4424,7 +4428,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>1.648274</v>
       </c>

--- a/output/pdf_financials_xlsx/CNTR.xlsx
+++ b/output/pdf_financials_xlsx/CNTR.xlsx
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.307795</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.049371</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
     </row>
     <row r="35">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.307795</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.049371</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
     </row>
     <row r="37">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.611983</v>
+        <v>0.304188</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.06433</v>
+        <v>0.014959</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.014265</v>
+        <v>0.012462</v>
       </c>
     </row>
     <row r="49">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CNTR.xlsx
+++ b/output/pdf_financials_xlsx/CNTR.xlsx
@@ -903,11 +903,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>1.507329</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>-0.552105</v>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2163,11 +2167,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n">
-        <v>1.507329</v>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>-0.552105</v>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -2176,10 +2184,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2194,10 +2200,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.000578</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.009202999999999999</v>
@@ -2212,10 +2216,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2230,10 +2232,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -2248,10 +2248,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.087548</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>-0.152765</v>
@@ -2266,10 +2264,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -2284,10 +2280,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.08697000000000001</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.143562</v>
@@ -2302,10 +2296,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.903661</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>-0.203642</v>
@@ -2320,10 +2312,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2338,10 +2328,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2356,10 +2344,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2374,10 +2360,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>-0.006303</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>-0.002157</v>
@@ -2392,10 +2376,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2410,10 +2392,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2428,10 +2408,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2446,10 +2424,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2464,10 +2440,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2482,10 +2456,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2500,10 +2472,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2540,10 +2510,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2558,10 +2526,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -2576,10 +2542,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2594,10 +2558,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2612,10 +2574,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2630,10 +2590,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2648,10 +2606,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2688,10 +2644,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -2728,10 +2682,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>3.855544</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>3.307795</v>
@@ -2746,10 +2698,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -2764,10 +2714,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-1.41739</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-3.258424</v>
@@ -2782,10 +2730,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>2.438154</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.049371</v>
@@ -2800,10 +2746,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.006303</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>-0.002157</v>
@@ -2845,7 +2789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5351,15 +5295,9 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>-2.298484</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>1.507329</v>
@@ -5389,10 +5327,8 @@
           <t>StockBasedCompensation</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="5" t="n">
+        <v>0.903661</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>-0.203642</v>
@@ -5420,10 +5356,8 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="5" t="n">
+        <v>0.054056</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0.002676</v>
@@ -5451,10 +5385,8 @@
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" s="5" t="n">
+        <v>-0.011193</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>-2.093928</v>
@@ -5513,10 +5445,8 @@
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>-0.002143</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>-0.000219</v>
@@ -5548,10 +5478,8 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="5" t="n">
+        <v>0.000578</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0.009202999999999999</v>
@@ -5577,10 +5505,8 @@
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="5" t="n">
+        <v>0.003185</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>-0.00421</v>
@@ -5610,10 +5536,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="5" t="n">
+        <v>-0.087548</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>-0.152765</v>
@@ -5668,10 +5592,8 @@
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="5" t="n">
+        <v>-1.471047</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>-0.817221</v>
@@ -5697,10 +5619,8 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="5" t="n">
+        <v>-3.511409</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>-2.351702</v>
@@ -5730,10 +5650,8 @@
           <t>PurchaseOfPPE</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>-0.006303</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>-0.002157</v>
@@ -5761,10 +5679,8 @@
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E95" s="5" t="n">
+        <v>-0.006303</v>
       </c>
       <c r="F95" s="5" t="n">
         <v>-0.002157</v>
@@ -5823,10 +5739,8 @@
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" s="5" t="n">
+        <v>3.688823</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5854,10 +5768,8 @@
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E98" s="5" t="n">
+        <v>-0.117454</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>-0.087344</v>
@@ -5885,10 +5797,8 @@
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="5" t="n">
+        <v>2.217776</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>-0.817221</v>
@@ -5914,10 +5824,8 @@
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="5" t="n">
+        <v>-3.635166</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>-2.441203</v>
@@ -5947,10 +5855,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="5" t="n">
+        <v>3.855544</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>3.307795</v>
@@ -5980,16 +5886,136 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="5" t="n">
+        <v>2.438154</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>0.049371</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>0.001803</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Due to related parties (note 13)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>-0.033159</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.087561</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Net proceeds from issuance of common shares and warrants</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>3.735447</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Net proceeds from sale of treasury shares</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>0.048042</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Purchase of treasury shares</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>-0.094666</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
